--- a/OI/TQ_2026 CQPM Technicien qualité - Bourges 5-6 Novembre  2026/V3_Formation_Salaries/Corriges_formateur/Corrige_TP_Butees.xlsx
+++ b/OI/TQ_2026 CQPM Technicien qualité - Bourges 5-6 Novembre  2026/V3_Formation_Salaries/Corriges_formateur/Corrige_TP_Butees.xlsx
@@ -1,18 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfaicentre-my.sharepoint.com/personal/s_jaubert_poleformation-uimmcvdl_fr/Documents/00FC/OI/TQ_2026 CQPM Technicien qualité - Bourges 5-6 Novembre  2026/V3_Formation_Salaries/Corriges_formateur/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_49EC4FF6939E90A8F426FE790D5E9CB4454E3E11" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C239590E-EADD-4A0F-851F-05DB0CE96565}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lot" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Henry" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Lot" sheetId="1" r:id="rId1"/>
+    <sheet name="Henry" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,165 +39,162 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
   <si>
-    <t xml:space="preserve">Echantillon</t>
+    <t>Echantillon</t>
   </si>
   <si>
-    <t xml:space="preserve">P1</t>
+    <t>P1</t>
   </si>
   <si>
-    <t xml:space="preserve">P2</t>
+    <t>P2</t>
   </si>
   <si>
-    <t xml:space="preserve">P3</t>
+    <t>P3</t>
   </si>
   <si>
-    <t xml:space="preserve">P4</t>
+    <t>P4</t>
   </si>
   <si>
-    <t xml:space="preserve">P5</t>
+    <t>P5</t>
   </si>
   <si>
-    <t xml:space="preserve">Moyenne</t>
+    <t>Moyenne</t>
   </si>
   <si>
-    <t xml:space="preserve">Etendue</t>
+    <t>Etendue</t>
   </si>
   <si>
-    <t xml:space="preserve">LC</t>
+    <t>LC</t>
   </si>
   <si>
-    <t xml:space="preserve">LCS AFNOR</t>
+    <t>LCS AFNOR</t>
   </si>
   <si>
-    <t xml:space="preserve">LCI AFNOR</t>
+    <t>LCI AFNOR</t>
   </si>
   <si>
-    <t xml:space="preserve">LSS AFNOR</t>
+    <t>LSS AFNOR</t>
   </si>
   <si>
-    <t xml:space="preserve">LSI AFNOR</t>
+    <t>LSI AFNOR</t>
   </si>
   <si>
-    <t xml:space="preserve">LCS 3σ</t>
+    <t>LCS 3σ</t>
   </si>
   <si>
-    <t xml:space="preserve">LCI 3σ</t>
+    <t>LCI 3σ</t>
   </si>
   <si>
-    <t xml:space="preserve">R barre</t>
+    <t>R barre</t>
   </si>
   <si>
-    <t xml:space="preserve">LC2 AFNOR</t>
+    <t>LC2 AFNOR</t>
   </si>
   <si>
-    <t xml:space="preserve">LS2 AFNOR</t>
+    <t>LS2 AFNOR</t>
   </si>
   <si>
-    <t xml:space="preserve">LCS R 3σ</t>
+    <t>LCS R 3σ</t>
   </si>
   <si>
-    <t xml:space="preserve">TI</t>
+    <t>TI</t>
   </si>
   <si>
-    <t xml:space="preserve">X double barre</t>
+    <t>X double barre</t>
   </si>
   <si>
-    <t xml:space="preserve">TS</t>
+    <t>TS</t>
   </si>
   <si>
-    <t xml:space="preserve">Nombre de mesures</t>
+    <t>Nombre de mesures</t>
   </si>
   <si>
-    <t xml:space="preserve">d2 (n = 5)</t>
+    <t>d2 (n = 5)</t>
   </si>
   <si>
-    <t xml:space="preserve">σ instantané</t>
+    <t>σ instantané</t>
   </si>
   <si>
-    <t xml:space="preserve">Écart-type s</t>
+    <t>Écart-type s</t>
   </si>
   <si>
-    <t xml:space="preserve">Cp</t>
+    <t>Cp</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus petite</t>
+    <t>Plus petite</t>
   </si>
   <si>
-    <t xml:space="preserve">Cpk</t>
+    <t>Cpk</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus grande</t>
+    <t>Plus grande</t>
   </si>
   <si>
-    <t xml:space="preserve">Pp</t>
+    <t>Pp</t>
   </si>
   <si>
-    <t xml:space="preserve">6 s</t>
+    <t>6 s</t>
   </si>
   <si>
-    <t xml:space="preserve">Ppk</t>
+    <t>Ppk</t>
   </si>
   <si>
-    <t xml:space="preserve">Coefficients n = 5</t>
+    <t>Coefficients n = 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Borne basse</t>
+    <t>Borne basse</t>
   </si>
   <si>
-    <t xml:space="preserve">Borne haute</t>
+    <t>Borne haute</t>
   </si>
   <si>
-    <t xml:space="preserve">Effectif</t>
+    <t>Effectif</t>
   </si>
   <si>
-    <t xml:space="preserve">A'c</t>
+    <t>A'c</t>
   </si>
   <si>
-    <t xml:space="preserve">Corrigé formateur. Lignes 8 à 11 (orange) : saisir les mesures des butées 1 à 20 du jour. Tant qu'une ligne est incomplète, ses moyenne et étendue affichent #N/A, ignorées par les calculs (AGREGAT).</t>
+    <t>Corrigé formateur. Lignes 8 à 11 (orange) : saisir les mesures des butées 1 à 20 du jour. Tant qu'une ligne est incomplète, ses moyenne et étendue affichent #N/A, ignorées par les calculs (AGREGAT).</t>
   </si>
   <si>
-    <t xml:space="preserve">A's</t>
+    <t>A's</t>
   </si>
   <si>
-    <t xml:space="preserve">D'c2</t>
+    <t>D'c2</t>
   </si>
   <si>
-    <t xml:space="preserve">D's2</t>
+    <t>D's2</t>
   </si>
   <si>
-    <t xml:space="preserve">A2</t>
+    <t>A2</t>
   </si>
   <si>
-    <t xml:space="preserve">D4</t>
+    <t>D4</t>
   </si>
   <si>
-    <t xml:space="preserve">Total</t>
+    <t>Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Rang</t>
+    <t>Rang</t>
   </si>
   <si>
-    <t xml:space="preserve">Valeur triée</t>
+    <t>Valeur triée</t>
   </si>
   <si>
-    <t xml:space="preserve">Fréquence</t>
+    <t>Fréquence</t>
   </si>
   <si>
-    <t xml:space="preserve">z</t>
+    <t>z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0"/>
-    <numFmt numFmtId="168" formatCode="0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,61 +203,23 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F4E9E"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -268,7 +243,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -276,85 +251,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -413,15 +333,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E9E"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -430,7 +368,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -438,7 +376,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="fr-FR" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -459,6 +397,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -467,7 +406,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!G1</c:f>
+              <c:f>Lot!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -477,12 +416,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="1f3864"/>
-            </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="1f3864"/>
+                <a:srgbClr val="1F3864"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -492,20 +428,28 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1f3864"/>
+                <a:srgbClr val="1F3864"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -513,8 +457,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -522,42 +467,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -566,7 +512,7 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>11.864</c:v>
+                  <c:v>11.863999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>11.862</c:v>
@@ -581,19 +527,36 @@
                   <c:v>11.91</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.902</c:v>
+                  <c:v>11.901999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-423C-4541-A0C0-A7F19223C277}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!P1</c:f>
+              <c:f>Lot!$P$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -603,12 +566,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="1f3864"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
-                <a:srgbClr val="1f3864"/>
+                <a:srgbClr val="1F3864"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
               <a:round/>
@@ -618,15 +578,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -634,8 +602,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -643,42 +612,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -687,46 +657,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.8866666666667</c:v>
+                  <c:v>11.886666666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-423C-4541-A0C0-A7F19223C277}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!Q1</c:f>
+              <c:f>Lot!$Q$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -736,12 +711,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="c00000"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
-                <a:srgbClr val="c00000"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -750,15 +722,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -766,8 +746,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -775,42 +756,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -819,46 +801,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.9163666666667</c:v>
+                  <c:v>11.916366666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-423C-4541-A0C0-A7F19223C277}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!R1</c:f>
+              <c:f>Lot!$R$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -868,12 +855,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="c00000"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
-                <a:srgbClr val="c00000"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -882,15 +866,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -898,8 +890,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -907,42 +900,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -951,46 +945,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.8569666666667</c:v>
+                  <c:v>11.856966666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-423C-4541-A0C0-A7F19223C277}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!S1</c:f>
+              <c:f>Lot!$S$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1000,12 +999,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="2e7d32"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
-                <a:srgbClr val="2e7d32"/>
+                <a:srgbClr val="2E7D32"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
               <a:round/>
@@ -1015,15 +1011,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1031,8 +1035,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1040,42 +1045,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1084,46 +1090,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.9055166666667</c:v>
+                  <c:v>11.905516666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-423C-4541-A0C0-A7F19223C277}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!T1</c:f>
+              <c:f>Lot!$T$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1133,12 +1144,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="2e7d32"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
-                <a:srgbClr val="2e7d32"/>
+                <a:srgbClr val="2E7D32"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
               <a:round/>
@@ -1148,15 +1156,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1164,8 +1180,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1173,42 +1190,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1217,46 +1235,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.8678166666667</c:v>
+                  <c:v>11.867816666666664</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-423C-4541-A0C0-A7F19223C277}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="6"/>
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!U1</c:f>
+              <c:f>Lot!$U$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1266,9 +1289,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="808080"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
@@ -1281,15 +1301,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1297,8 +1325,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1306,42 +1335,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1350,46 +1380,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.9155166666667</c:v>
+                  <c:v>11.915516666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-423C-4541-A0C0-A7F19223C277}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="7"/>
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!V1</c:f>
+              <c:f>Lot!$V$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1399,9 +1434,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="808080"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
@@ -1414,15 +1446,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1430,8 +1470,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1439,42 +1480,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1483,40 +1525,53 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.8578166666667</c:v>
+                  <c:v>11.857816666666665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-423C-4541-A0C0-A7F19223C277}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1525,6 +1580,7 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="48243291"/>
         <c:axId val="18517867"/>
       </c:lineChart>
@@ -1552,13 +1608,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="18517867"/>
@@ -1592,13 +1649,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="48243291"/>
@@ -1626,37 +1684,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1665,7 +1732,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1673,7 +1740,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="fr-FR" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1694,6 +1761,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1702,7 +1770,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!H1</c:f>
+              <c:f>Lot!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1712,12 +1780,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="1f3864"/>
-            </a:solidFill>
             <a:ln w="19080">
               <a:solidFill>
-                <a:srgbClr val="1f3864"/>
+                <a:srgbClr val="1F3864"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1727,20 +1792,28 @@
             <c:size val="6"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1f3864"/>
+                <a:srgbClr val="1F3864"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1748,8 +1821,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1757,42 +1831,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1801,34 +1876,51 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.0400000000000009</c:v>
+                  <c:v>4.0000000000000924E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0500000000000007</c:v>
+                  <c:v>5.0000000000000711E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0500000000000007</c:v>
+                  <c:v>5.0000000000000711E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0399999999999992</c:v>
+                  <c:v>3.9999999999999147E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0399999999999992</c:v>
+                  <c:v>3.9999999999999147E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0800000000000001</c:v>
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7927-41CE-A915-991AFDFF4C33}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!W1</c:f>
+              <c:f>Lot!$W$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1838,12 +1930,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="1f3864"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
-                <a:srgbClr val="1f3864"/>
+                <a:srgbClr val="1F3864"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
               <a:round/>
@@ -1853,15 +1942,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1869,8 +1966,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1878,42 +1976,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1922,46 +2021,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0500000000000001</c:v>
+                  <c:v>5.0000000000000121E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7927-41CE-A915-991AFDFF4C33}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!X1</c:f>
+              <c:f>Lot!$X$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1971,12 +2075,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="c00000"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
-                <a:srgbClr val="c00000"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1985,15 +2086,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2001,8 +2110,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2010,42 +2120,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2054,46 +2165,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.118</c:v>
+                  <c:v>0.11800000000000029</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7927-41CE-A915-991AFDFF4C33}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!Y1</c:f>
+              <c:f>Lot!$Y$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2103,12 +2219,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="2e7d32"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
-                <a:srgbClr val="2e7d32"/>
+                <a:srgbClr val="2E7D32"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
               <a:round/>
@@ -2118,15 +2231,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2134,8 +2255,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2143,42 +2265,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2187,46 +2310,51 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0905000000000002</c:v>
+                  <c:v>9.0500000000000219E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7927-41CE-A915-991AFDFF4C33}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!Z1</c:f>
+              <c:f>Lot!$Z$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2236,9 +2364,6 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="808080"/>
-            </a:solidFill>
             <a:ln w="15840">
               <a:solidFill>
                 <a:srgbClr val="808080"/>
@@ -2251,15 +2376,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2267,8 +2400,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2276,42 +2410,43 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$A$2:$A$11</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.000</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2320,40 +2455,53 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1057</c:v>
+                  <c:v>0.10570000000000025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7927-41CE-A915-991AFDFF4C33}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -2362,6 +2510,7 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="22095888"/>
         <c:axId val="60374515"/>
       </c:lineChart>
@@ -2389,13 +2538,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="60374515"/>
@@ -2412,7 +2562,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2429,13 +2579,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="22095888"/>
@@ -2463,37 +2614,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2502,7 +2662,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2510,7 +2670,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="fr-FR" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2531,6 +2691,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -2540,7 +2701,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Lot!L12</c:f>
+              <c:f>Lot!$L$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2551,7 +2712,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -2559,15 +2720,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2575,8 +2744,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2584,63 +2754,64 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Lot!$J$13:$J$29</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>11.825</c:v>
+                  <c:v>11.824999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.835</c:v>
+                  <c:v>11.834999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.845</c:v>
+                  <c:v>11.844999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.855</c:v>
+                  <c:v>11.854999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.865</c:v>
+                  <c:v>11.864999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.875</c:v>
+                  <c:v>11.874999999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.885</c:v>
+                  <c:v>11.884999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.895</c:v>
+                  <c:v>11.894999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.905</c:v>
+                  <c:v>11.904999999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.915</c:v>
+                  <c:v>11.914999999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11.925</c:v>
+                  <c:v>11.924999999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11.935</c:v>
+                  <c:v>11.934999999999997</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>11.945</c:v>
+                  <c:v>11.944999999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>11.955</c:v>
+                  <c:v>11.954999999999997</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>11.965</c:v>
+                  <c:v>11.964999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>11.975</c:v>
+                  <c:v>11.974999999999996</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>11.985</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>11.984999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2702,9 +2873,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-648F-4B27-9787-7F067F2D8354}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:gapWidth val="0"/>
-        <c:overlap val="0"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="5"/>
         <c:axId val="74015222"/>
         <c:axId val="91888679"/>
       </c:barChart>
@@ -2732,13 +2915,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="91888679"/>
@@ -2782,13 +2966,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="74015222"/>
@@ -2804,25 +2989,33 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2831,7 +3024,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2839,7 +3032,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="fr-FR" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2860,6 +3053,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -2867,20 +3061,9 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>"Mesures"</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Mesures</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Mesures</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ffffff"/>
-            </a:solidFill>
             <a:ln w="47520">
               <a:noFill/>
             </a:ln>
@@ -2893,15 +3076,23 @@
             </c:spPr>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2909,8 +3100,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -3013,6 +3205,66 @@
                 <c:pt idx="29">
                   <c:v>11.93</c:v>
                 </c:pt>
+                <c:pt idx="30">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>#N/A</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3023,100 +3275,173 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
-                  <c:v>-2.12804523418498</c:v>
+                  <c:v>-2.128045234184984</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-1.64485362695147</c:v>
+                  <c:v>-1.6448536269514726</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.38299412710064</c:v>
+                  <c:v>-1.3829941271006392</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.19181617168139</c:v>
+                  <c:v>-1.1918161716813944</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1.03643338949379</c:v>
+                  <c:v>-1.0364333894937898</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.902734791643865</c:v>
+                  <c:v>-0.90273479164386372</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.783500375389774</c:v>
+                  <c:v>-0.78350037538977446</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.674489750196082</c:v>
+                  <c:v>-0.67448975019608193</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.572967548495464</c:v>
+                  <c:v>-0.57296754849546372</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.477040428489443</c:v>
+                  <c:v>-0.47704042848944361</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.385320466407568</c:v>
+                  <c:v>-0.38532046640756784</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.296737838259898</c:v>
+                  <c:v>-0.29673783825989802</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.210428394247925</c:v>
+                  <c:v>-0.21042839424792467</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.125661346855074</c:v>
+                  <c:v>-0.12566134685507402</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.0417892978164538</c:v>
+                  <c:v>-4.178929781645381E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.041789297816454</c:v>
+                  <c:v>4.1789297816453949E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.125661346855074</c:v>
+                  <c:v>0.12566134685507416</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.210428394247925</c:v>
+                  <c:v>0.21042839424792484</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.296737838259898</c:v>
+                  <c:v>0.29673783825989819</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.385320466407568</c:v>
+                  <c:v>0.38532046640756784</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.477040428489443</c:v>
+                  <c:v>0.47704042848944361</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.572967548495464</c:v>
+                  <c:v>0.57296754849546372</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.674489750196082</c:v>
+                  <c:v>0.67448975019608193</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.783500375389774</c:v>
+                  <c:v>0.78350037538977446</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.902734791643865</c:v>
+                  <c:v>0.90273479164386372</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.03643338949379</c:v>
+                  <c:v>1.0364333894937898</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.19181617168139</c:v>
+                  <c:v>1.1918161716813944</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.38299412710064</c:v>
+                  <c:v>1.3829941271006372</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.64485362695147</c:v>
+                  <c:v>1.6448536269514715</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.12804523418498</c:v>
+                  <c:v>2.128045234184984</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>#N/A</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-72D7-4E44-BF6D-C49FD055EAD6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="18339227"/>
         <c:axId val="74074771"/>
       </c:scatterChart>
@@ -3144,7 +3469,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3152,7 +3477,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="fr-FR" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3188,13 +3513,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="74074771"/>
@@ -3225,7 +3551,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3233,7 +3559,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="fr-FR" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -3269,13 +3595,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="18339227"/>
@@ -3291,23 +3618,29 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3321,14 +3654,20 @@
       <xdr:row>47</xdr:row>
       <xdr:rowOff>42840</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="6095880"/>
-        <a:ext cx="7199640" cy="3239640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3351,14 +3690,20 @@
       <xdr:row>47</xdr:row>
       <xdr:rowOff>42840</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7052400" y="6095880"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3381,14 +3726,20 @@
       <xdr:row>63</xdr:row>
       <xdr:rowOff>74880</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="9715680"/>
-        <a:ext cx="5759640" cy="2699640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3402,7 +3753,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -3416,14 +3767,20 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>21960</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 1"/>
+        <xdr:cNvPr id="3" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3057480" y="190440"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3437,41 +3794,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -3479,12 +3836,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -3513,7 +3870,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -3534,7 +3891,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -3585,7 +3942,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -3603,607 +3960,606 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="16" style="0" width="10.51"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="16" max="26" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:26" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3">
         <v>11.87</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3">
         <v>11.86</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3">
         <v>11.84</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3">
         <v>11.88</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3">
         <v>11.87</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <f aca="false">IF(COUNT(B2:F2)&lt;5,NA(),AVERAGE(B2:F2))</f>
-        <v>11.864</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <f aca="false">IF(COUNT(B2:F2)&lt;5,NA(),MAX(B2:F2)-MIN(B2:F2))</f>
-        <v>0.0400000000000009</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="G2" s="4">
+        <f t="shared" ref="G2:G11" si="0">IF(COUNT(B2:F2)&lt;5,NA(),AVERAGE(B2:F2))</f>
+        <v>11.863999999999999</v>
+      </c>
+      <c r="H2" s="5">
+        <f t="shared" ref="H2:H11" si="1">IF(COUNT(B2:F2)&lt;5,NA(),MAX(B2:F2)-MIN(B2:F2))</f>
+        <v>4.0000000000000924E-2</v>
+      </c>
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2">
         <v>11.85</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="3" t="n">
-        <f aca="false">_xlfn.AGGREGATE(1,6,G2:G11)</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U2" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W2" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X2" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z2" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="N2" s="4">
+        <f>_xlfn.AGGREGATE(1,6,G2:G11)</f>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="P2" s="4">
+        <f t="shared" ref="P2:P11" si="2">$N$2</f>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q2" s="4">
+        <f t="shared" ref="Q2:Q11" si="3">$N$2+$N$12*$N$3</f>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R2" s="4">
+        <f t="shared" ref="R2:R11" si="4">$N$2-$N$12*$N$3</f>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S2" s="4">
+        <f t="shared" ref="S2:S11" si="5">$N$2+$N$13*$N$3</f>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T2" s="4">
+        <f t="shared" ref="T2:T11" si="6">$N$2-$N$13*$N$3</f>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U2" s="4">
+        <f t="shared" ref="U2:U11" si="7">$N$2+$N$16*$N$3</f>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V2" s="4">
+        <f t="shared" ref="V2:V11" si="8">$N$2-$N$16*$N$3</f>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W2" s="4">
+        <f t="shared" ref="W2:W11" si="9">$N$3</f>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X2" s="4">
+        <f t="shared" ref="X2:X11" si="10">$N$14*$N$3</f>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y2" s="4">
+        <f t="shared" ref="Y2:Y11" si="11">$N$15*$N$3</f>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z2" s="4">
+        <f t="shared" ref="Z2:Z11" si="12">$N$17*$N$3</f>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3">
         <v>11.87</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3">
         <v>11.85</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3">
         <v>11.86</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3">
         <v>11.84</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3">
         <v>11.89</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <f aca="false">IF(COUNT(B3:F3)&lt;5,NA(),AVERAGE(B3:F3))</f>
+      <c r="G3" s="4">
+        <f t="shared" si="0"/>
         <v>11.862</v>
       </c>
-      <c r="H3" s="4" t="n">
-        <f aca="false">IF(COUNT(B3:F3)&lt;5,NA(),MAX(B3:F3)-MIN(B3:F3))</f>
-        <v>0.0500000000000007</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="H3" s="5">
+        <f t="shared" si="1"/>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="J3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3">
         <v>12</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="3" t="n">
-        <f aca="false">_xlfn.AGGREGATE(1,6,H2:H11)</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="N3" s="4">
+        <f>_xlfn.AGGREGATE(1,6,H2:H11)</f>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="P3" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q3" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R3" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S3" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T3" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U3" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V3" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W3" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X3" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y3" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z3" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3">
         <v>11.91</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3">
         <v>11.9</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3">
         <v>11.86</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3">
         <v>11.88</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3">
         <v>11.87</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <f aca="false">IF(COUNT(B4:F4)&lt;5,NA(),AVERAGE(B4:F4))</f>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
         <v>11.884</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <f aca="false">IF(COUNT(B4:F4)&lt;5,NA(),MAX(B4:F4)-MIN(B4:F4))</f>
-        <v>0.0500000000000007</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="H4" s="5">
+        <f t="shared" si="1"/>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="6" t="n">
-        <f aca="false">COUNT(B2:F11)</f>
+      <c r="K4" s="6">
+        <f>COUNT(B2:F11)</f>
         <v>30</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="0" t="n">
-        <v>2.326</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="N4">
+        <v>2.3260000000000001</v>
+      </c>
+      <c r="P4" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R4" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S4" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T4" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U4" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V4" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W4" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X4" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y4" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3">
         <v>11.89</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3">
         <v>11.91</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3">
         <v>11.89</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3">
         <v>11.88</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3">
         <v>11.92</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <f aca="false">IF(COUNT(B5:F5)&lt;5,NA(),AVERAGE(B5:F5))</f>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
         <v>11.898</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <f aca="false">IF(COUNT(B5:F5)&lt;5,NA(),MAX(B5:F5)-MIN(B5:F5))</f>
-        <v>0.0399999999999992</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="H5" s="5">
+        <f t="shared" si="1"/>
+        <v>3.9999999999999147E-2</v>
+      </c>
+      <c r="J5" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <f aca="false">AVERAGE(B2:F11)</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="M5" s="5" t="s">
+      <c r="K5" s="4">
+        <f>AVERAGE(B2:F11)</f>
+        <v>11.886666666666667</v>
+      </c>
+      <c r="M5" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <f aca="false">N3/N4</f>
-        <v>0.0214961306964747</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="N5" s="4">
+        <f>N3/N4</f>
+        <v>2.1496130696474686E-2</v>
+      </c>
+      <c r="P5" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R5" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S5" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T5" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U5" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V5" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W5" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X5" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y5" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3">
         <v>11.91</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3">
         <v>11.92</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3">
         <v>11.93</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3">
         <v>11.89</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3">
         <v>11.9</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <f aca="false">IF(COUNT(B6:F6)&lt;5,NA(),AVERAGE(B6:F6))</f>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
         <v>11.91</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <f aca="false">IF(COUNT(B6:F6)&lt;5,NA(),MAX(B6:F6)-MIN(B6:F6))</f>
-        <v>0.0399999999999992</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="H6" s="5">
+        <f t="shared" si="1"/>
+        <v>3.9999999999999147E-2</v>
+      </c>
+      <c r="J6" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <f aca="false">_xlfn.STDEV.S(B2:F11)</f>
-        <v>0.0264357820900508</v>
-      </c>
-      <c r="M6" s="5" t="s">
+      <c r="K6" s="4">
+        <f>_xlfn.STDEV.S(B2:F11)</f>
+        <v>2.6435782090050829E-2</v>
+      </c>
+      <c r="M6" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="7" t="n">
-        <f aca="false">($K$3-$K$2)/(6*N5)</f>
+      <c r="N6" s="7">
+        <f>($K$3-$K$2)/(6*N5)</f>
         <v>1.163</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="P6" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R6" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S6" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T6" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U6" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V6" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W6" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X6" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y6" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3">
         <v>11.85</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3">
         <v>11.91</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3">
         <v>11.92</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3">
         <v>11.93</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3">
         <v>11.9</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <f aca="false">IF(COUNT(B7:F7)&lt;5,NA(),AVERAGE(B7:F7))</f>
-        <v>11.902</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <f aca="false">IF(COUNT(B7:F7)&lt;5,NA(),MAX(B7:F7)-MIN(B7:F7))</f>
-        <v>0.0800000000000001</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="G7" s="4">
+        <f t="shared" si="0"/>
+        <v>11.901999999999999</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="1"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="J7" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="4" t="n">
-        <f aca="false">MIN(B2:F11)</f>
+      <c r="K7" s="5">
+        <f>MIN(B2:F11)</f>
         <v>11.84</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="7" t="n">
-        <f aca="false">MIN($K$3-N2,N2-$K$2)/(3*N5)</f>
-        <v>0.568577777777755</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="N7" s="7">
+        <f>MIN($K$3-N2,N2-$K$2)/(3*N5)</f>
+        <v>0.56857777777775509</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q7" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R7" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S7" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T7" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U7" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V7" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W7" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X7" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y7" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="8"/>
@@ -4211,75 +4567,75 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
-      <c r="G8" s="3" t="e">
-        <f aca="false">IF(COUNT(B8:F8)&lt;5,NA(),AVERAGE(B8:F8))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H8" s="4" t="e">
-        <f aca="false">IF(COUNT(B8:F8)&lt;5,NA(),MAX(B8:F8)-MIN(B8:F8))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="G8" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H8" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J8" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <f aca="false">MAX(B2:F11)</f>
+      <c r="K8" s="5">
+        <f>MAX(B2:F11)</f>
         <v>11.93</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" t="s">
         <v>30</v>
       </c>
-      <c r="N8" s="7" t="n">
-        <f aca="false">($K$3-$K$2)/(6*K6)</f>
-        <v>0.945687928385855</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="N8" s="7">
+        <f>($K$3-$K$2)/(6*K6)</f>
+        <v>0.94568792838585514</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q8" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R8" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S8" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T8" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U8" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V8" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W8" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X8" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y8" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="8"/>
@@ -4287,75 +4643,75 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
-      <c r="G9" s="3" t="e">
-        <f aca="false">IF(COUNT(B9:F9)&lt;5,NA(),AVERAGE(B9:F9))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H9" s="4" t="e">
-        <f aca="false">IF(COUNT(B9:F9)&lt;5,NA(),MAX(B9:F9)-MIN(B9:F9))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="G9" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H9" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J9" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="3" t="n">
-        <f aca="false">6*K6</f>
-        <v>0.158614692540305</v>
-      </c>
-      <c r="M9" s="5" t="s">
+      <c r="K9" s="4">
+        <f>6*K6</f>
+        <v>0.15861469254030497</v>
+      </c>
+      <c r="M9" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="7" t="n">
-        <f aca="false">MIN($K$3-K5,K5-$K$2)/(3*K6)</f>
-        <v>0.4623363205442</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U9" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="N9" s="7">
+        <f>MIN($K$3-K5,K5-$K$2)/(3*K6)</f>
+        <v>0.46233632054419982</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q9" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R9" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S9" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T9" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U9" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V9" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W9" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X9" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y9" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="8"/>
@@ -4363,61 +4719,61 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="3" t="e">
-        <f aca="false">IF(COUNT(B10:F10)&lt;5,NA(),AVERAGE(B10:F10))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H10" s="4" t="e">
-        <f aca="false">IF(COUNT(B10:F10)&lt;5,NA(),MAX(B10:F10)-MIN(B10:F10))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="G10" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H10" s="5" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P10" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q10" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R10" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S10" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T10" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U10" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V10" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W10" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X10" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y10" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="8"/>
@@ -4425,394 +4781,394 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
-      <c r="G11" s="3" t="e">
-        <f aca="false">IF(COUNT(B11:F11)&lt;5,NA(),AVERAGE(B11:F11))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H11" s="4" t="e">
-        <f aca="false">IF(COUNT(B11:F11)&lt;5,NA(),MAX(B11:F11)-MIN(B11:F11))</f>
+      <c r="G11" s="4" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H11" s="5" t="e">
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="P11" s="3" t="n">
-        <f aca="false">$N$2</f>
-        <v>11.8866666666667</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <f aca="false">$N$2+$N$12*$N$3</f>
-        <v>11.9163666666667</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <f aca="false">$N$2-$N$12*$N$3</f>
-        <v>11.8569666666667</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <f aca="false">$N$2+$N$13*$N$3</f>
-        <v>11.9055166666667</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <f aca="false">$N$2-$N$13*$N$3</f>
-        <v>11.8678166666667</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <f aca="false">$N$2+$N$16*$N$3</f>
-        <v>11.9155166666667</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <f aca="false">$N$2-$N$16*$N$3</f>
-        <v>11.8578166666667</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <f aca="false">$N$3</f>
-        <v>0.0500000000000001</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <f aca="false">$N$14*$N$3</f>
-        <v>0.118</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <f aca="false">$N$15*$N$3</f>
-        <v>0.0905000000000002</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <f aca="false">$N$17*$N$3</f>
-        <v>0.1057</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J12" s="1" t="s">
+      <c r="P11" s="4">
+        <f t="shared" si="2"/>
+        <v>11.886666666666665</v>
+      </c>
+      <c r="Q11" s="4">
+        <f t="shared" si="3"/>
+        <v>11.916366666666665</v>
+      </c>
+      <c r="R11" s="4">
+        <f t="shared" si="4"/>
+        <v>11.856966666666665</v>
+      </c>
+      <c r="S11" s="4">
+        <f t="shared" si="5"/>
+        <v>11.905516666666665</v>
+      </c>
+      <c r="T11" s="4">
+        <f t="shared" si="6"/>
+        <v>11.867816666666664</v>
+      </c>
+      <c r="U11" s="4">
+        <f t="shared" si="7"/>
+        <v>11.915516666666665</v>
+      </c>
+      <c r="V11" s="4">
+        <f t="shared" si="8"/>
+        <v>11.857816666666665</v>
+      </c>
+      <c r="W11" s="4">
+        <f t="shared" si="9"/>
+        <v>5.0000000000000121E-2</v>
+      </c>
+      <c r="X11" s="4">
+        <f t="shared" si="10"/>
+        <v>0.11800000000000029</v>
+      </c>
+      <c r="Y11" s="4">
+        <f t="shared" si="11"/>
+        <v>9.0500000000000219E-2</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="12"/>
+        <v>0.10570000000000025</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="J12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="0" t="n">
-        <v>0.594</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="N12">
+        <v>0.59399999999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="J13" s="2" t="n">
-        <v>11.825</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <f aca="false">J13+0.01</f>
-        <v>11.835</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J13,$B$2:$F$11,"&lt;"&amp;K13)</f>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="J13" s="3">
+        <v>11.824999999999999</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" ref="K13:K29" si="13">J13+0.01</f>
+        <v>11.834999999999999</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" ref="L13:L29" si="14">COUNTIFS($B$2:$F$11,"&gt;="&amp;J13,$B$2:$F$11,"&lt;"&amp;K13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" t="s">
         <v>39</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13">
         <v>0.377</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="J14" s="4" t="n">
-        <f aca="false">K13</f>
-        <v>11.835</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <f aca="false">J14+0.01</f>
-        <v>11.845</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J14,$B$2:$F$11,"&lt;"&amp;K14)</f>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="J14" s="5">
+        <f t="shared" ref="J14:J29" si="15">K13</f>
+        <v>11.834999999999999</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="13"/>
+        <v>11.844999999999999</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" t="s">
         <v>40</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14">
         <v>2.36</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="J15" s="4" t="n">
-        <f aca="false">K14</f>
-        <v>11.845</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <f aca="false">J15+0.01</f>
-        <v>11.855</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J15,$B$2:$F$11,"&lt;"&amp;K15)</f>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="J15" s="5">
+        <f t="shared" si="15"/>
+        <v>11.844999999999999</v>
+      </c>
+      <c r="K15" s="5">
+        <f t="shared" si="13"/>
+        <v>11.854999999999999</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="M15" t="s">
         <v>41</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15">
         <v>1.81</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="J16" s="4" t="n">
-        <f aca="false">K15</f>
-        <v>11.855</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <f aca="false">J16+0.01</f>
-        <v>11.865</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J16,$B$2:$F$11,"&lt;"&amp;K16)</f>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="J16" s="5">
+        <f t="shared" si="15"/>
+        <v>11.854999999999999</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" si="13"/>
+        <v>11.864999999999998</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" t="s">
         <v>42</v>
       </c>
-      <c r="N16" s="0" t="n">
-        <v>0.577</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="J17" s="4" t="n">
-        <f aca="false">K16</f>
-        <v>11.865</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <f aca="false">J17+0.01</f>
-        <v>11.875</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J17,$B$2:$F$11,"&lt;"&amp;K17)</f>
+      <c r="N16">
+        <v>0.57699999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="J17" s="5">
+        <f t="shared" si="15"/>
+        <v>11.864999999999998</v>
+      </c>
+      <c r="K17" s="5">
+        <f t="shared" si="13"/>
+        <v>11.874999999999998</v>
+      </c>
+      <c r="L17" s="6">
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="M17" t="s">
         <v>43</v>
       </c>
-      <c r="N17" s="0" t="n">
-        <v>2.114</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J18" s="4" t="n">
-        <f aca="false">K17</f>
-        <v>11.875</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <f aca="false">J18+0.01</f>
-        <v>11.885</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J18,$B$2:$F$11,"&lt;"&amp;K18)</f>
+      <c r="N17">
+        <v>2.1139999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J18" s="5">
+        <f t="shared" si="15"/>
+        <v>11.874999999999998</v>
+      </c>
+      <c r="K18" s="5">
+        <f t="shared" si="13"/>
+        <v>11.884999999999998</v>
+      </c>
+      <c r="L18" s="6">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J19" s="4" t="n">
-        <f aca="false">K18</f>
-        <v>11.885</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <f aca="false">J19+0.01</f>
-        <v>11.895</v>
-      </c>
-      <c r="L19" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J19,$B$2:$F$11,"&lt;"&amp;K19)</f>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J19" s="5">
+        <f t="shared" si="15"/>
+        <v>11.884999999999998</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="13"/>
+        <v>11.894999999999998</v>
+      </c>
+      <c r="L19" s="6">
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J20" s="4" t="n">
-        <f aca="false">K19</f>
-        <v>11.895</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <f aca="false">J20+0.01</f>
-        <v>11.905</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J20,$B$2:$F$11,"&lt;"&amp;K20)</f>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J20" s="5">
+        <f t="shared" si="15"/>
+        <v>11.894999999999998</v>
+      </c>
+      <c r="K20" s="5">
+        <f t="shared" si="13"/>
+        <v>11.904999999999998</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J21" s="4" t="n">
-        <f aca="false">K20</f>
-        <v>11.905</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <f aca="false">J21+0.01</f>
-        <v>11.915</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J21,$B$2:$F$11,"&lt;"&amp;K21)</f>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J21" s="5">
+        <f t="shared" si="15"/>
+        <v>11.904999999999998</v>
+      </c>
+      <c r="K21" s="5">
+        <f t="shared" si="13"/>
+        <v>11.914999999999997</v>
+      </c>
+      <c r="L21" s="6">
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J22" s="4" t="n">
-        <f aca="false">K21</f>
-        <v>11.915</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <f aca="false">J22+0.01</f>
-        <v>11.925</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J22,$B$2:$F$11,"&lt;"&amp;K22)</f>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J22" s="5">
+        <f t="shared" si="15"/>
+        <v>11.914999999999997</v>
+      </c>
+      <c r="K22" s="5">
+        <f t="shared" si="13"/>
+        <v>11.924999999999997</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J23" s="4" t="n">
-        <f aca="false">K22</f>
-        <v>11.925</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <f aca="false">J23+0.01</f>
-        <v>11.935</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J23,$B$2:$F$11,"&lt;"&amp;K23)</f>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J23" s="5">
+        <f t="shared" si="15"/>
+        <v>11.924999999999997</v>
+      </c>
+      <c r="K23" s="5">
+        <f t="shared" si="13"/>
+        <v>11.934999999999997</v>
+      </c>
+      <c r="L23" s="6">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J24" s="4" t="n">
-        <f aca="false">K23</f>
-        <v>11.935</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <f aca="false">J24+0.01</f>
-        <v>11.945</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J24,$B$2:$F$11,"&lt;"&amp;K24)</f>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J24" s="5">
+        <f t="shared" si="15"/>
+        <v>11.934999999999997</v>
+      </c>
+      <c r="K24" s="5">
+        <f t="shared" si="13"/>
+        <v>11.944999999999997</v>
+      </c>
+      <c r="L24" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J25" s="4" t="n">
-        <f aca="false">K24</f>
-        <v>11.945</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <f aca="false">J25+0.01</f>
-        <v>11.955</v>
-      </c>
-      <c r="L25" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J25,$B$2:$F$11,"&lt;"&amp;K25)</f>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J25" s="5">
+        <f t="shared" si="15"/>
+        <v>11.944999999999997</v>
+      </c>
+      <c r="K25" s="5">
+        <f t="shared" si="13"/>
+        <v>11.954999999999997</v>
+      </c>
+      <c r="L25" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J26" s="4" t="n">
-        <f aca="false">K25</f>
-        <v>11.955</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <f aca="false">J26+0.01</f>
-        <v>11.965</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J26,$B$2:$F$11,"&lt;"&amp;K26)</f>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J26" s="5">
+        <f t="shared" si="15"/>
+        <v>11.954999999999997</v>
+      </c>
+      <c r="K26" s="5">
+        <f t="shared" si="13"/>
+        <v>11.964999999999996</v>
+      </c>
+      <c r="L26" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J27" s="4" t="n">
-        <f aca="false">K26</f>
-        <v>11.965</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <f aca="false">J27+0.01</f>
-        <v>11.975</v>
-      </c>
-      <c r="L27" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J27,$B$2:$F$11,"&lt;"&amp;K27)</f>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J27" s="5">
+        <f t="shared" si="15"/>
+        <v>11.964999999999996</v>
+      </c>
+      <c r="K27" s="5">
+        <f t="shared" si="13"/>
+        <v>11.974999999999996</v>
+      </c>
+      <c r="L27" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J28" s="4" t="n">
-        <f aca="false">K27</f>
-        <v>11.975</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <f aca="false">J28+0.01</f>
-        <v>11.985</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J28,$B$2:$F$11,"&lt;"&amp;K28)</f>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J28" s="5">
+        <f t="shared" si="15"/>
+        <v>11.974999999999996</v>
+      </c>
+      <c r="K28" s="5">
+        <f t="shared" si="13"/>
+        <v>11.984999999999996</v>
+      </c>
+      <c r="L28" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J29" s="4" t="n">
-        <f aca="false">K28</f>
-        <v>11.985</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <f aca="false">J29+0.01</f>
-        <v>11.995</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <f aca="false">COUNTIFS($B$2:$F$11,"&gt;="&amp;J29,$B$2:$F$11,"&lt;"&amp;K29)</f>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J29" s="5">
+        <f t="shared" si="15"/>
+        <v>11.984999999999996</v>
+      </c>
+      <c r="K29" s="5">
+        <f t="shared" si="13"/>
+        <v>11.994999999999996</v>
+      </c>
+      <c r="L29" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K30" s="0" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K30" t="s">
         <v>44</v>
       </c>
-      <c r="L30" s="6" t="n">
-        <f aca="false">SUM(L13:L29)</f>
+      <c r="L30" s="6">
+        <f>SUM(L13:L29)</f>
         <v>30</v>
       </c>
     </row>
@@ -4820,897 +5176,884 @@
   <mergeCells count="1">
     <mergeCell ref="A13:H17"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D51"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n">
-        <f aca="false">IF(A2&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A2))</f>
+      <c r="B2" s="5">
+        <f>IF(A2&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A2))</f>
         <v>11.84</v>
       </c>
-      <c r="C2" s="4" t="n">
-        <f aca="false">IF(A2&gt;Lot!$K$4,NA(),(A2-0.5)/Lot!$K$4)</f>
-        <v>0.0166666666666667</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <f aca="false">IF(A2&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C2))</f>
-        <v>-2.12804523418498</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="C2" s="5">
+        <f>IF(A2&gt;Lot!$K$4,NA(),(A2-0.5)/Lot!$K$4)</f>
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="D2" s="5">
+        <f>IF(A2&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C2))</f>
+        <v>-2.128045234184984</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n">
-        <f aca="false">IF(A3&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A3))</f>
+      <c r="B3" s="5">
+        <f>IF(A3&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A3))</f>
         <v>11.84</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <f aca="false">IF(A3&gt;Lot!$K$4,NA(),(A3-0.5)/Lot!$K$4)</f>
+      <c r="C3" s="5">
+        <f>IF(A3&gt;Lot!$K$4,NA(),(A3-0.5)/Lot!$K$4)</f>
         <v>0.05</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <f aca="false">IF(A3&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C3))</f>
-        <v>-1.64485362695147</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="D3" s="5">
+        <f>IF(A3&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C3))</f>
+        <v>-1.6448536269514726</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="n">
-        <f aca="false">IF(A4&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A4))</f>
+      <c r="B4" s="5">
+        <f>IF(A4&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A4))</f>
         <v>11.85</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <f aca="false">IF(A4&gt;Lot!$K$4,NA(),(A4-0.5)/Lot!$K$4)</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <f aca="false">IF(A4&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C4))</f>
-        <v>-1.38299412710064</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="C4" s="5">
+        <f>IF(A4&gt;Lot!$K$4,NA(),(A4-0.5)/Lot!$K$4)</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="D4" s="5">
+        <f>IF(A4&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C4))</f>
+        <v>-1.3829941271006392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n">
-        <f aca="false">IF(A5&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A5))</f>
+      <c r="B5" s="5">
+        <f>IF(A5&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A5))</f>
         <v>11.85</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <f aca="false">IF(A5&gt;Lot!$K$4,NA(),(A5-0.5)/Lot!$K$4)</f>
-        <v>0.116666666666667</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <f aca="false">IF(A5&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C5))</f>
-        <v>-1.19181617168139</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="C5" s="5">
+        <f>IF(A5&gt;Lot!$K$4,NA(),(A5-0.5)/Lot!$K$4)</f>
+        <v>0.11666666666666667</v>
+      </c>
+      <c r="D5" s="5">
+        <f>IF(A5&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C5))</f>
+        <v>-1.1918161716813944</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <f aca="false">IF(A6&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A6))</f>
+      <c r="B6" s="5">
+        <f>IF(A6&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A6))</f>
         <v>11.86</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <f aca="false">IF(A6&gt;Lot!$K$4,NA(),(A6-0.5)/Lot!$K$4)</f>
+      <c r="C6" s="5">
+        <f>IF(A6&gt;Lot!$K$4,NA(),(A6-0.5)/Lot!$K$4)</f>
         <v>0.15</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <f aca="false">IF(A6&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C6))</f>
-        <v>-1.03643338949379</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="D6" s="5">
+        <f>IF(A6&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C6))</f>
+        <v>-1.0364333894937898</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <f aca="false">IF(A7&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A7))</f>
+      <c r="B7" s="5">
+        <f>IF(A7&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A7))</f>
         <v>11.86</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <f aca="false">IF(A7&gt;Lot!$K$4,NA(),(A7-0.5)/Lot!$K$4)</f>
-        <v>0.183333333333333</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <f aca="false">IF(A7&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C7))</f>
-        <v>-0.902734791643865</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="C7" s="5">
+        <f>IF(A7&gt;Lot!$K$4,NA(),(A7-0.5)/Lot!$K$4)</f>
+        <v>0.18333333333333332</v>
+      </c>
+      <c r="D7" s="5">
+        <f>IF(A7&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C7))</f>
+        <v>-0.90273479164386372</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <f aca="false">IF(A8&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A8))</f>
+      <c r="B8" s="5">
+        <f>IF(A8&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A8))</f>
         <v>11.86</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <f aca="false">IF(A8&gt;Lot!$K$4,NA(),(A8-0.5)/Lot!$K$4)</f>
-        <v>0.216666666666667</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <f aca="false">IF(A8&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C8))</f>
-        <v>-0.783500375389774</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="C8" s="5">
+        <f>IF(A8&gt;Lot!$K$4,NA(),(A8-0.5)/Lot!$K$4)</f>
+        <v>0.21666666666666667</v>
+      </c>
+      <c r="D8" s="5">
+        <f>IF(A8&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C8))</f>
+        <v>-0.78350037538977446</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <f aca="false">IF(A9&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A9))</f>
+      <c r="B9" s="5">
+        <f>IF(A9&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A9))</f>
         <v>11.87</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <f aca="false">IF(A9&gt;Lot!$K$4,NA(),(A9-0.5)/Lot!$K$4)</f>
+      <c r="C9" s="5">
+        <f>IF(A9&gt;Lot!$K$4,NA(),(A9-0.5)/Lot!$K$4)</f>
         <v>0.25</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <f aca="false">IF(A9&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C9))</f>
-        <v>-0.674489750196082</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="D9" s="5">
+        <f>IF(A9&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C9))</f>
+        <v>-0.67448975019608193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <f aca="false">IF(A10&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A10))</f>
+      <c r="B10" s="5">
+        <f>IF(A10&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A10))</f>
         <v>11.87</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <f aca="false">IF(A10&gt;Lot!$K$4,NA(),(A10-0.5)/Lot!$K$4)</f>
-        <v>0.283333333333333</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <f aca="false">IF(A10&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C10))</f>
-        <v>-0.572967548495464</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="C10" s="5">
+        <f>IF(A10&gt;Lot!$K$4,NA(),(A10-0.5)/Lot!$K$4)</f>
+        <v>0.28333333333333333</v>
+      </c>
+      <c r="D10" s="5">
+        <f>IF(A10&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C10))</f>
+        <v>-0.57296754849546372</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <f aca="false">IF(A11&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A11))</f>
+      <c r="B11" s="5">
+        <f>IF(A11&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A11))</f>
         <v>11.87</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <f aca="false">IF(A11&gt;Lot!$K$4,NA(),(A11-0.5)/Lot!$K$4)</f>
-        <v>0.316666666666667</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <f aca="false">IF(A11&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C11))</f>
-        <v>-0.477040428489443</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="C11" s="5">
+        <f>IF(A11&gt;Lot!$K$4,NA(),(A11-0.5)/Lot!$K$4)</f>
+        <v>0.31666666666666665</v>
+      </c>
+      <c r="D11" s="5">
+        <f>IF(A11&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C11))</f>
+        <v>-0.47704042848944361</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <f aca="false">IF(A12&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A12))</f>
+      <c r="B12" s="5">
+        <f>IF(A12&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A12))</f>
         <v>11.87</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <f aca="false">IF(A12&gt;Lot!$K$4,NA(),(A12-0.5)/Lot!$K$4)</f>
+      <c r="C12" s="5">
+        <f>IF(A12&gt;Lot!$K$4,NA(),(A12-0.5)/Lot!$K$4)</f>
         <v>0.35</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <f aca="false">IF(A12&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C12))</f>
-        <v>-0.385320466407568</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="D12" s="5">
+        <f>IF(A12&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C12))</f>
+        <v>-0.38532046640756784</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <f aca="false">IF(A13&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A13))</f>
+      <c r="B13" s="5">
+        <f>IF(A13&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A13))</f>
         <v>11.88</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <f aca="false">IF(A13&gt;Lot!$K$4,NA(),(A13-0.5)/Lot!$K$4)</f>
-        <v>0.383333333333333</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <f aca="false">IF(A13&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C13))</f>
-        <v>-0.296737838259898</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="C13" s="5">
+        <f>IF(A13&gt;Lot!$K$4,NA(),(A13-0.5)/Lot!$K$4)</f>
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="D13" s="5">
+        <f>IF(A13&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C13))</f>
+        <v>-0.29673783825989802</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <f aca="false">IF(A14&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A14))</f>
+      <c r="B14" s="5">
+        <f>IF(A14&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A14))</f>
         <v>11.88</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <f aca="false">IF(A14&gt;Lot!$K$4,NA(),(A14-0.5)/Lot!$K$4)</f>
-        <v>0.416666666666667</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <f aca="false">IF(A14&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C14))</f>
-        <v>-0.210428394247925</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="C14" s="5">
+        <f>IF(A14&gt;Lot!$K$4,NA(),(A14-0.5)/Lot!$K$4)</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D14" s="5">
+        <f>IF(A14&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C14))</f>
+        <v>-0.21042839424792467</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <f aca="false">IF(A15&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A15))</f>
+      <c r="B15" s="5">
+        <f>IF(A15&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A15))</f>
         <v>11.88</v>
       </c>
-      <c r="C15" s="4" t="n">
-        <f aca="false">IF(A15&gt;Lot!$K$4,NA(),(A15-0.5)/Lot!$K$4)</f>
+      <c r="C15" s="5">
+        <f>IF(A15&gt;Lot!$K$4,NA(),(A15-0.5)/Lot!$K$4)</f>
         <v>0.45</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <f aca="false">IF(A15&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C15))</f>
-        <v>-0.125661346855074</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="D15" s="5">
+        <f>IF(A15&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C15))</f>
+        <v>-0.12566134685507402</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <f aca="false">IF(A16&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A16))</f>
+      <c r="B16" s="5">
+        <f>IF(A16&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A16))</f>
         <v>11.89</v>
       </c>
-      <c r="C16" s="4" t="n">
-        <f aca="false">IF(A16&gt;Lot!$K$4,NA(),(A16-0.5)/Lot!$K$4)</f>
-        <v>0.483333333333333</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <f aca="false">IF(A16&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C16))</f>
-        <v>-0.0417892978164538</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="C16" s="5">
+        <f>IF(A16&gt;Lot!$K$4,NA(),(A16-0.5)/Lot!$K$4)</f>
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D16" s="5">
+        <f>IF(A16&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C16))</f>
+        <v>-4.178929781645381E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <f aca="false">IF(A17&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A17))</f>
+      <c r="B17" s="5">
+        <f>IF(A17&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A17))</f>
         <v>11.89</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <f aca="false">IF(A17&gt;Lot!$K$4,NA(),(A17-0.5)/Lot!$K$4)</f>
-        <v>0.516666666666667</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <f aca="false">IF(A17&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C17))</f>
-        <v>0.041789297816454</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="C17" s="5">
+        <f>IF(A17&gt;Lot!$K$4,NA(),(A17-0.5)/Lot!$K$4)</f>
+        <v>0.51666666666666672</v>
+      </c>
+      <c r="D17" s="5">
+        <f>IF(A17&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C17))</f>
+        <v>4.1789297816453949E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <f aca="false">IF(A18&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A18))</f>
+      <c r="B18" s="5">
+        <f>IF(A18&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A18))</f>
         <v>11.89</v>
       </c>
-      <c r="C18" s="4" t="n">
-        <f aca="false">IF(A18&gt;Lot!$K$4,NA(),(A18-0.5)/Lot!$K$4)</f>
-        <v>0.55</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <f aca="false">IF(A18&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C18))</f>
-        <v>0.125661346855074</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="C18" s="5">
+        <f>IF(A18&gt;Lot!$K$4,NA(),(A18-0.5)/Lot!$K$4)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D18" s="5">
+        <f>IF(A18&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C18))</f>
+        <v>0.12566134685507416</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <f aca="false">IF(A19&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A19))</f>
+      <c r="B19" s="5">
+        <f>IF(A19&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A19))</f>
         <v>11.89</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <f aca="false">IF(A19&gt;Lot!$K$4,NA(),(A19-0.5)/Lot!$K$4)</f>
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <f aca="false">IF(A19&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C19))</f>
-        <v>0.210428394247925</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="C19" s="5">
+        <f>IF(A19&gt;Lot!$K$4,NA(),(A19-0.5)/Lot!$K$4)</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D19" s="5">
+        <f>IF(A19&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C19))</f>
+        <v>0.21042839424792484</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <f aca="false">IF(A20&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A20))</f>
+      <c r="B20" s="5">
+        <f>IF(A20&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A20))</f>
         <v>11.9</v>
       </c>
-      <c r="C20" s="4" t="n">
-        <f aca="false">IF(A20&gt;Lot!$K$4,NA(),(A20-0.5)/Lot!$K$4)</f>
-        <v>0.616666666666667</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <f aca="false">IF(A20&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C20))</f>
-        <v>0.296737838259898</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="C20" s="5">
+        <f>IF(A20&gt;Lot!$K$4,NA(),(A20-0.5)/Lot!$K$4)</f>
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="D20" s="5">
+        <f>IF(A20&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C20))</f>
+        <v>0.29673783825989819</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <f aca="false">IF(A21&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A21))</f>
+      <c r="B21" s="5">
+        <f>IF(A21&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A21))</f>
         <v>11.9</v>
       </c>
-      <c r="C21" s="4" t="n">
-        <f aca="false">IF(A21&gt;Lot!$K$4,NA(),(A21-0.5)/Lot!$K$4)</f>
+      <c r="C21" s="5">
+        <f>IF(A21&gt;Lot!$K$4,NA(),(A21-0.5)/Lot!$K$4)</f>
         <v>0.65</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <f aca="false">IF(A21&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C21))</f>
-        <v>0.385320466407568</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="D21" s="5">
+        <f>IF(A21&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C21))</f>
+        <v>0.38532046640756784</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <f aca="false">IF(A22&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A22))</f>
+      <c r="B22" s="5">
+        <f>IF(A22&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A22))</f>
         <v>11.9</v>
       </c>
-      <c r="C22" s="4" t="n">
-        <f aca="false">IF(A22&gt;Lot!$K$4,NA(),(A22-0.5)/Lot!$K$4)</f>
-        <v>0.683333333333333</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <f aca="false">IF(A22&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C22))</f>
-        <v>0.477040428489443</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="C22" s="5">
+        <f>IF(A22&gt;Lot!$K$4,NA(),(A22-0.5)/Lot!$K$4)</f>
+        <v>0.68333333333333335</v>
+      </c>
+      <c r="D22" s="5">
+        <f>IF(A22&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C22))</f>
+        <v>0.47704042848944361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <f aca="false">IF(A23&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A23))</f>
+      <c r="B23" s="5">
+        <f>IF(A23&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A23))</f>
         <v>11.91</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <f aca="false">IF(A23&gt;Lot!$K$4,NA(),(A23-0.5)/Lot!$K$4)</f>
-        <v>0.716666666666667</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <f aca="false">IF(A23&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C23))</f>
-        <v>0.572967548495464</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="C23" s="5">
+        <f>IF(A23&gt;Lot!$K$4,NA(),(A23-0.5)/Lot!$K$4)</f>
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="D23" s="5">
+        <f>IF(A23&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C23))</f>
+        <v>0.57296754849546372</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <f aca="false">IF(A24&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A24))</f>
+      <c r="B24" s="5">
+        <f>IF(A24&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A24))</f>
         <v>11.91</v>
       </c>
-      <c r="C24" s="4" t="n">
-        <f aca="false">IF(A24&gt;Lot!$K$4,NA(),(A24-0.5)/Lot!$K$4)</f>
+      <c r="C24" s="5">
+        <f>IF(A24&gt;Lot!$K$4,NA(),(A24-0.5)/Lot!$K$4)</f>
         <v>0.75</v>
       </c>
-      <c r="D24" s="4" t="n">
-        <f aca="false">IF(A24&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C24))</f>
-        <v>0.674489750196082</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="D24" s="5">
+        <f>IF(A24&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C24))</f>
+        <v>0.67448975019608193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <f aca="false">IF(A25&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A25))</f>
+      <c r="B25" s="5">
+        <f>IF(A25&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A25))</f>
         <v>11.91</v>
       </c>
-      <c r="C25" s="4" t="n">
-        <f aca="false">IF(A25&gt;Lot!$K$4,NA(),(A25-0.5)/Lot!$K$4)</f>
-        <v>0.783333333333333</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <f aca="false">IF(A25&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C25))</f>
-        <v>0.783500375389774</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="C25" s="5">
+        <f>IF(A25&gt;Lot!$K$4,NA(),(A25-0.5)/Lot!$K$4)</f>
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="D25" s="5">
+        <f>IF(A25&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C25))</f>
+        <v>0.78350037538977446</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <f aca="false">IF(A26&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A26))</f>
+      <c r="B26" s="5">
+        <f>IF(A26&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A26))</f>
         <v>11.91</v>
       </c>
-      <c r="C26" s="4" t="n">
-        <f aca="false">IF(A26&gt;Lot!$K$4,NA(),(A26-0.5)/Lot!$K$4)</f>
-        <v>0.816666666666667</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <f aca="false">IF(A26&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C26))</f>
-        <v>0.902734791643865</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="C26" s="5">
+        <f>IF(A26&gt;Lot!$K$4,NA(),(A26-0.5)/Lot!$K$4)</f>
+        <v>0.81666666666666665</v>
+      </c>
+      <c r="D26" s="5">
+        <f>IF(A26&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C26))</f>
+        <v>0.90273479164386372</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <f aca="false">IF(A27&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A27))</f>
+      <c r="B27" s="5">
+        <f>IF(A27&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A27))</f>
         <v>11.92</v>
       </c>
-      <c r="C27" s="4" t="n">
-        <f aca="false">IF(A27&gt;Lot!$K$4,NA(),(A27-0.5)/Lot!$K$4)</f>
+      <c r="C27" s="5">
+        <f>IF(A27&gt;Lot!$K$4,NA(),(A27-0.5)/Lot!$K$4)</f>
         <v>0.85</v>
       </c>
-      <c r="D27" s="4" t="n">
-        <f aca="false">IF(A27&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C27))</f>
-        <v>1.03643338949379</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="D27" s="5">
+        <f>IF(A27&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C27))</f>
+        <v>1.0364333894937898</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="n">
-        <f aca="false">IF(A28&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A28))</f>
+      <c r="B28" s="5">
+        <f>IF(A28&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A28))</f>
         <v>11.92</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <f aca="false">IF(A28&gt;Lot!$K$4,NA(),(A28-0.5)/Lot!$K$4)</f>
-        <v>0.883333333333333</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <f aca="false">IF(A28&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C28))</f>
-        <v>1.19181617168139</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="C28" s="5">
+        <f>IF(A28&gt;Lot!$K$4,NA(),(A28-0.5)/Lot!$K$4)</f>
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="D28" s="5">
+        <f>IF(A28&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C28))</f>
+        <v>1.1918161716813944</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="n">
-        <f aca="false">IF(A29&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A29))</f>
+      <c r="B29" s="5">
+        <f>IF(A29&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A29))</f>
         <v>11.92</v>
       </c>
-      <c r="C29" s="4" t="n">
-        <f aca="false">IF(A29&gt;Lot!$K$4,NA(),(A29-0.5)/Lot!$K$4)</f>
-        <v>0.916666666666667</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <f aca="false">IF(A29&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C29))</f>
-        <v>1.38299412710064</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="C29" s="5">
+        <f>IF(A29&gt;Lot!$K$4,NA(),(A29-0.5)/Lot!$K$4)</f>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D29" s="5">
+        <f>IF(A29&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C29))</f>
+        <v>1.3829941271006372</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="n">
-        <f aca="false">IF(A30&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A30))</f>
+      <c r="B30" s="5">
+        <f>IF(A30&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A30))</f>
         <v>11.93</v>
       </c>
-      <c r="C30" s="4" t="n">
-        <f aca="false">IF(A30&gt;Lot!$K$4,NA(),(A30-0.5)/Lot!$K$4)</f>
+      <c r="C30" s="5">
+        <f>IF(A30&gt;Lot!$K$4,NA(),(A30-0.5)/Lot!$K$4)</f>
         <v>0.95</v>
       </c>
-      <c r="D30" s="4" t="n">
-        <f aca="false">IF(A30&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C30))</f>
-        <v>1.64485362695147</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="D30" s="5">
+        <f>IF(A30&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C30))</f>
+        <v>1.6448536269514715</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <f aca="false">IF(A31&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A31))</f>
+      <c r="B31" s="5">
+        <f>IF(A31&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A31))</f>
         <v>11.93</v>
       </c>
-      <c r="C31" s="4" t="n">
-        <f aca="false">IF(A31&gt;Lot!$K$4,NA(),(A31-0.5)/Lot!$K$4)</f>
-        <v>0.983333333333333</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <f aca="false">IF(A31&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C31))</f>
-        <v>2.12804523418498</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="C31" s="5">
+        <f>IF(A31&gt;Lot!$K$4,NA(),(A31-0.5)/Lot!$K$4)</f>
+        <v>0.98333333333333328</v>
+      </c>
+      <c r="D31" s="5">
+        <f>IF(A31&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C31))</f>
+        <v>2.128045234184984</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="e">
-        <f aca="false">IF(A32&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A32))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C32" s="4" t="e">
-        <f aca="false">IF(A32&gt;Lot!$K$4,NA(),(A32-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D32" s="4" t="e">
-        <f aca="false">IF(A32&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C32))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="B32" s="5" t="e">
+        <f>IF(A32&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A32))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C32" s="5" t="e">
+        <f>IF(A32&gt;Lot!$K$4,NA(),(A32-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D32" s="5" t="e">
+        <f>IF(A32&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C32))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="e">
-        <f aca="false">IF(A33&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A33))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C33" s="4" t="e">
-        <f aca="false">IF(A33&gt;Lot!$K$4,NA(),(A33-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D33" s="4" t="e">
-        <f aca="false">IF(A33&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C33))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="B33" s="5" t="e">
+        <f>IF(A33&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A33))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C33" s="5" t="e">
+        <f>IF(A33&gt;Lot!$K$4,NA(),(A33-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D33" s="5" t="e">
+        <f>IF(A33&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C33))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="e">
-        <f aca="false">IF(A34&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A34))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C34" s="4" t="e">
-        <f aca="false">IF(A34&gt;Lot!$K$4,NA(),(A34-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D34" s="4" t="e">
-        <f aca="false">IF(A34&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C34))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="B34" s="5" t="e">
+        <f>IF(A34&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A34))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C34" s="5" t="e">
+        <f>IF(A34&gt;Lot!$K$4,NA(),(A34-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D34" s="5" t="e">
+        <f>IF(A34&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C34))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="e">
-        <f aca="false">IF(A35&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A35))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C35" s="4" t="e">
-        <f aca="false">IF(A35&gt;Lot!$K$4,NA(),(A35-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D35" s="4" t="e">
-        <f aca="false">IF(A35&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C35))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="B35" s="5" t="e">
+        <f>IF(A35&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A35))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C35" s="5" t="e">
+        <f>IF(A35&gt;Lot!$K$4,NA(),(A35-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D35" s="5" t="e">
+        <f>IF(A35&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C35))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="e">
-        <f aca="false">IF(A36&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A36))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C36" s="4" t="e">
-        <f aca="false">IF(A36&gt;Lot!$K$4,NA(),(A36-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D36" s="4" t="e">
-        <f aca="false">IF(A36&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C36))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="B36" s="5" t="e">
+        <f>IF(A36&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A36))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C36" s="5" t="e">
+        <f>IF(A36&gt;Lot!$K$4,NA(),(A36-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D36" s="5" t="e">
+        <f>IF(A36&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C36))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="e">
-        <f aca="false">IF(A37&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A37))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C37" s="4" t="e">
-        <f aca="false">IF(A37&gt;Lot!$K$4,NA(),(A37-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D37" s="4" t="e">
-        <f aca="false">IF(A37&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C37))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="B37" s="5" t="e">
+        <f>IF(A37&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A37))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C37" s="5" t="e">
+        <f>IF(A37&gt;Lot!$K$4,NA(),(A37-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D37" s="5" t="e">
+        <f>IF(A37&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C37))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="e">
-        <f aca="false">IF(A38&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A38))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C38" s="4" t="e">
-        <f aca="false">IF(A38&gt;Lot!$K$4,NA(),(A38-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D38" s="4" t="e">
-        <f aca="false">IF(A38&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C38))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="B38" s="5" t="e">
+        <f>IF(A38&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A38))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C38" s="5" t="e">
+        <f>IF(A38&gt;Lot!$K$4,NA(),(A38-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D38" s="5" t="e">
+        <f>IF(A38&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C38))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="e">
-        <f aca="false">IF(A39&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A39))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C39" s="4" t="e">
-        <f aca="false">IF(A39&gt;Lot!$K$4,NA(),(A39-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D39" s="4" t="e">
-        <f aca="false">IF(A39&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C39))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="B39" s="5" t="e">
+        <f>IF(A39&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A39))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C39" s="5" t="e">
+        <f>IF(A39&gt;Lot!$K$4,NA(),(A39-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D39" s="5" t="e">
+        <f>IF(A39&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C39))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="e">
-        <f aca="false">IF(A40&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A40))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C40" s="4" t="e">
-        <f aca="false">IF(A40&gt;Lot!$K$4,NA(),(A40-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D40" s="4" t="e">
-        <f aca="false">IF(A40&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C40))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="B40" s="5" t="e">
+        <f>IF(A40&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A40))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C40" s="5" t="e">
+        <f>IF(A40&gt;Lot!$K$4,NA(),(A40-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D40" s="5" t="e">
+        <f>IF(A40&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C40))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="e">
-        <f aca="false">IF(A41&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A41))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C41" s="4" t="e">
-        <f aca="false">IF(A41&gt;Lot!$K$4,NA(),(A41-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D41" s="4" t="e">
-        <f aca="false">IF(A41&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C41))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="B41" s="5" t="e">
+        <f>IF(A41&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A41))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C41" s="5" t="e">
+        <f>IF(A41&gt;Lot!$K$4,NA(),(A41-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D41" s="5" t="e">
+        <f>IF(A41&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C41))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="e">
-        <f aca="false">IF(A42&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A42))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C42" s="4" t="e">
-        <f aca="false">IF(A42&gt;Lot!$K$4,NA(),(A42-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D42" s="4" t="e">
-        <f aca="false">IF(A42&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C42))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="B42" s="5" t="e">
+        <f>IF(A42&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A42))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C42" s="5" t="e">
+        <f>IF(A42&gt;Lot!$K$4,NA(),(A42-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D42" s="5" t="e">
+        <f>IF(A42&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C42))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="e">
-        <f aca="false">IF(A43&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A43))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C43" s="4" t="e">
-        <f aca="false">IF(A43&gt;Lot!$K$4,NA(),(A43-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D43" s="4" t="e">
-        <f aca="false">IF(A43&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C43))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="B43" s="5" t="e">
+        <f>IF(A43&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A43))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C43" s="5" t="e">
+        <f>IF(A43&gt;Lot!$K$4,NA(),(A43-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D43" s="5" t="e">
+        <f>IF(A43&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C43))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="4" t="e">
-        <f aca="false">IF(A44&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A44))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C44" s="4" t="e">
-        <f aca="false">IF(A44&gt;Lot!$K$4,NA(),(A44-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D44" s="4" t="e">
-        <f aca="false">IF(A44&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C44))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="B44" s="5" t="e">
+        <f>IF(A44&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A44))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C44" s="5" t="e">
+        <f>IF(A44&gt;Lot!$K$4,NA(),(A44-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D44" s="5" t="e">
+        <f>IF(A44&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C44))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="e">
-        <f aca="false">IF(A45&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A45))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C45" s="4" t="e">
-        <f aca="false">IF(A45&gt;Lot!$K$4,NA(),(A45-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D45" s="4" t="e">
-        <f aca="false">IF(A45&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C45))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="B45" s="5" t="e">
+        <f>IF(A45&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A45))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C45" s="5" t="e">
+        <f>IF(A45&gt;Lot!$K$4,NA(),(A45-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D45" s="5" t="e">
+        <f>IF(A45&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C45))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="e">
-        <f aca="false">IF(A46&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A46))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C46" s="4" t="e">
-        <f aca="false">IF(A46&gt;Lot!$K$4,NA(),(A46-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D46" s="4" t="e">
-        <f aca="false">IF(A46&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C46))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="B46" s="5" t="e">
+        <f>IF(A46&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A46))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C46" s="5" t="e">
+        <f>IF(A46&gt;Lot!$K$4,NA(),(A46-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D46" s="5" t="e">
+        <f>IF(A46&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C46))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="e">
-        <f aca="false">IF(A47&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A47))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C47" s="4" t="e">
-        <f aca="false">IF(A47&gt;Lot!$K$4,NA(),(A47-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D47" s="4" t="e">
-        <f aca="false">IF(A47&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C47))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="B47" s="5" t="e">
+        <f>IF(A47&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A47))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C47" s="5" t="e">
+        <f>IF(A47&gt;Lot!$K$4,NA(),(A47-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D47" s="5" t="e">
+        <f>IF(A47&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C47))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="e">
-        <f aca="false">IF(A48&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A48))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C48" s="4" t="e">
-        <f aca="false">IF(A48&gt;Lot!$K$4,NA(),(A48-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D48" s="4" t="e">
-        <f aca="false">IF(A48&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C48))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="B48" s="5" t="e">
+        <f>IF(A48&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A48))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C48" s="5" t="e">
+        <f>IF(A48&gt;Lot!$K$4,NA(),(A48-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D48" s="5" t="e">
+        <f>IF(A48&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C48))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="e">
-        <f aca="false">IF(A49&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A49))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C49" s="4" t="e">
-        <f aca="false">IF(A49&gt;Lot!$K$4,NA(),(A49-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D49" s="4" t="e">
-        <f aca="false">IF(A49&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C49))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="B49" s="5" t="e">
+        <f>IF(A49&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A49))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C49" s="5" t="e">
+        <f>IF(A49&gt;Lot!$K$4,NA(),(A49-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D49" s="5" t="e">
+        <f>IF(A49&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C49))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="e">
-        <f aca="false">IF(A50&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A50))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C50" s="4" t="e">
-        <f aca="false">IF(A50&gt;Lot!$K$4,NA(),(A50-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D50" s="4" t="e">
-        <f aca="false">IF(A50&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C50))</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="B50" s="5" t="e">
+        <f>IF(A50&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A50))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C50" s="5" t="e">
+        <f>IF(A50&gt;Lot!$K$4,NA(),(A50-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D50" s="5" t="e">
+        <f>IF(A50&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C50))</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="e">
-        <f aca="false">IF(A51&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A51))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C51" s="4" t="e">
-        <f aca="false">IF(A51&gt;Lot!$K$4,NA(),(A51-0.5)/Lot!$K$4)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D51" s="4" t="e">
-        <f aca="false">IF(A51&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C51))</f>
+      <c r="B51" s="5" t="e">
+        <f>IF(A51&gt;Lot!$K$4,NA(),SMALL(Lot!$B$2:$F$11,A51))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C51" s="5" t="e">
+        <f>IF(A51&gt;Lot!$K$4,NA(),(A51-0.5)/Lot!$K$4)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D51" s="5" t="e">
+        <f>IF(A51&gt;Lot!$K$4,NA(),_xlfn.NORM.S.INV(C51))</f>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>